--- a/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/3_fold/6.xlsx
+++ b/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/3_fold/6.xlsx
@@ -426,13 +426,13 @@
         <v>-16.49871876876686</v>
       </c>
       <c r="E2">
-        <v>-11.60080678043512</v>
+        <v>-6.336011956065575</v>
       </c>
       <c r="F2">
-        <v>-2.801931951419728</v>
+        <v>-2.15820855094176</v>
       </c>
       <c r="G2">
-        <v>-8.925493457641057</v>
+        <v>-8.826160538735225</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -449,13 +449,13 @@
         <v>-16.29132662420852</v>
       </c>
       <c r="E3">
-        <v>-12.15549050468664</v>
+        <v>-7.216347303156692</v>
       </c>
       <c r="F3">
-        <v>-2.578306341336016</v>
+        <v>-2.037747127895689</v>
       </c>
       <c r="G3">
-        <v>-8.899737413345527</v>
+        <v>-8.277162840321266</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -472,13 +472,13 @@
         <v>-16.07464188544748</v>
       </c>
       <c r="E4">
-        <v>-13.13605003851552</v>
+        <v>-8.591241825099498</v>
       </c>
       <c r="F4">
-        <v>-3.172778863402691</v>
+        <v>-2.183625447178648</v>
       </c>
       <c r="G4">
-        <v>-8.28263848264322</v>
+        <v>-7.775876724219284</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -495,13 +495,13 @@
         <v>-15.8648094910313</v>
       </c>
       <c r="E5">
-        <v>-13.39375643734403</v>
+        <v>-9.231577106732102</v>
       </c>
       <c r="F5">
-        <v>-2.888456932256804</v>
+        <v>-1.997869412944924</v>
       </c>
       <c r="G5">
-        <v>-7.9877483281871</v>
+        <v>-7.834814366454928</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -518,13 +518,13 @@
         <v>-15.65388654262988</v>
       </c>
       <c r="E6">
-        <v>-14.33571525873152</v>
+        <v>-10.52580592117627</v>
       </c>
       <c r="F6">
-        <v>-2.575246621507387</v>
+        <v>-2.011182836723066</v>
       </c>
       <c r="G6">
-        <v>-7.802169076892175</v>
+        <v>-6.47922211067078</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -541,13 +541,13 @@
         <v>-15.44083081637027</v>
       </c>
       <c r="E7">
-        <v>-14.27846176185255</v>
+        <v>-9.146686332984313</v>
       </c>
       <c r="F7">
-        <v>-3.008064737814453</v>
+        <v>-1.810680124857728</v>
       </c>
       <c r="G7">
-        <v>-7.546098379429549</v>
+        <v>-8.444570507151131</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -564,13 +564,13 @@
         <v>-15.22006715167164</v>
       </c>
       <c r="E8">
-        <v>-16.24198544920838</v>
+        <v>-11.08469659778093</v>
       </c>
       <c r="F8">
-        <v>-2.643671427436906</v>
+        <v>-1.878780271074582</v>
       </c>
       <c r="G8">
-        <v>-7.780892200711279</v>
+        <v>-7.456359421496525</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -587,13 +587,13 @@
         <v>-14.98746516867466</v>
       </c>
       <c r="E9">
-        <v>-16.69868205288193</v>
+        <v>-11.5581711976529</v>
       </c>
       <c r="F9">
-        <v>-2.586665933010663</v>
+        <v>-1.554035038290061</v>
       </c>
       <c r="G9">
-        <v>-7.86260639625711</v>
+        <v>-7.448278379835163</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -610,13 +610,13 @@
         <v>-14.743603248489</v>
       </c>
       <c r="E10">
-        <v>-17.7264690421368</v>
+        <v>-11.9828333761962</v>
       </c>
       <c r="F10">
-        <v>-2.530972538935362</v>
+        <v>-1.468570348563371</v>
       </c>
       <c r="G10">
-        <v>-7.3025779601063</v>
+        <v>-6.646907863325945</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -633,13 +633,13 @@
         <v>-14.50004277908572</v>
       </c>
       <c r="E11">
-        <v>-18.31017575630349</v>
+        <v>-13.02362161432709</v>
       </c>
       <c r="F11">
-        <v>-2.122120644246641</v>
+        <v>-1.762697794884701</v>
       </c>
       <c r="G11">
-        <v>-6.862358167021713</v>
+        <v>-6.821340507790143</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -656,13 +656,13 @@
         <v>-14.27377778137334</v>
       </c>
       <c r="E12">
-        <v>-18.73952490544472</v>
+        <v>-14.81524895682576</v>
       </c>
       <c r="F12">
-        <v>-2.30106515933806</v>
+        <v>-1.105767078924925</v>
       </c>
       <c r="G12">
-        <v>-6.283297404565634</v>
+        <v>-6.484754032266903</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -679,13 +679,13 @@
         <v>-14.08437136944316</v>
       </c>
       <c r="E13">
-        <v>-19.52910510494812</v>
+        <v>-14.71202692029492</v>
       </c>
       <c r="F13">
-        <v>-1.915909464409102</v>
+        <v>-1.140880214629091</v>
       </c>
       <c r="G13">
-        <v>-6.170924246780612</v>
+        <v>-6.050347557149276</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -702,13 +702,13 @@
         <v>-13.94908583543658</v>
       </c>
       <c r="E14">
-        <v>-19.37762764939155</v>
+        <v>-14.67010230793191</v>
       </c>
       <c r="F14">
-        <v>-1.846052196479067</v>
+        <v>-1.288280475296787</v>
       </c>
       <c r="G14">
-        <v>-5.167537620373986</v>
+        <v>-5.532157795523776</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -725,13 +725,13 @@
         <v>-13.87073943165178</v>
       </c>
       <c r="E15">
-        <v>-20.54299420747345</v>
+        <v>-16.27473084475784</v>
       </c>
       <c r="F15">
-        <v>-1.566637378112171</v>
+        <v>-0.7839216116715746</v>
       </c>
       <c r="G15">
-        <v>-5.992376594211099</v>
+        <v>-4.658220120793732</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -748,13 +748,13 @@
         <v>-13.83654455217009</v>
       </c>
       <c r="E16">
-        <v>-20.73276443923888</v>
+        <v>-16.27531048943082</v>
       </c>
       <c r="F16">
-        <v>-1.126912720307873</v>
+        <v>-0.6405154573226172</v>
       </c>
       <c r="G16">
-        <v>-5.461176388616262</v>
+        <v>-4.042051453387961</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -771,13 +771,13 @@
         <v>-13.8215262994071</v>
       </c>
       <c r="E17">
-        <v>-21.27736778034934</v>
+        <v>-17.49222919561604</v>
       </c>
       <c r="F17">
-        <v>-1.247520636151122</v>
+        <v>-0.5967402421139555</v>
       </c>
       <c r="G17">
-        <v>-5.125887646944416</v>
+        <v>-3.975512798594149</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -794,13 +794,13 @@
         <v>-13.79438301694672</v>
       </c>
       <c r="E18">
-        <v>-22.64907425659074</v>
+        <v>-17.87745742250055</v>
       </c>
       <c r="F18">
-        <v>-1.137670834591453</v>
+        <v>-0.3614720179928906</v>
       </c>
       <c r="G18">
-        <v>-4.613299328371362</v>
+        <v>-4.149614388504421</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -817,13 +817,13 @@
         <v>-13.72420146766535</v>
       </c>
       <c r="E19">
-        <v>-23.37034242568843</v>
+        <v>-19.7885096815295</v>
       </c>
       <c r="F19">
-        <v>-0.6209432277666588</v>
+        <v>0.1970250404986614</v>
       </c>
       <c r="G19">
-        <v>-4.707457864599313</v>
+        <v>-2.967799289167696</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -840,13 +840,13 @@
         <v>-13.58633262032415</v>
       </c>
       <c r="E20">
-        <v>-24.16436052971934</v>
+        <v>-20.77058625415095</v>
       </c>
       <c r="F20">
-        <v>-0.5733908739496739</v>
+        <v>0.5266979742390717</v>
       </c>
       <c r="G20">
-        <v>-3.872564763959433</v>
+        <v>-3.932608128405195</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -863,13 +863,13 @@
         <v>-13.36526140653864</v>
       </c>
       <c r="E21">
-        <v>-24.84799707981329</v>
+        <v>-21.01388757716105</v>
       </c>
       <c r="F21">
-        <v>-0.2555593093390044</v>
+        <v>0.6276497241128438</v>
       </c>
       <c r="G21">
-        <v>-4.23147093750844</v>
+        <v>-3.273521548628312</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -886,13 +886,13 @@
         <v>-13.05686783821991</v>
       </c>
       <c r="E22">
-        <v>-26.04986313839702</v>
+        <v>-22.63844139962073</v>
       </c>
       <c r="F22">
-        <v>-0.09093149572315841</v>
+        <v>0.5246835003146327</v>
       </c>
       <c r="G22">
-        <v>-4.249966955436348</v>
+        <v>-2.686733972883573</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -909,13 +909,13 @@
         <v>-12.66995807272992</v>
       </c>
       <c r="E23">
-        <v>-26.32501774757708</v>
+        <v>-22.18903111062552</v>
       </c>
       <c r="F23">
-        <v>0.1324359702963367</v>
+        <v>1.003672187027463</v>
       </c>
       <c r="G23">
-        <v>-4.495966973368512</v>
+        <v>-3.673236817039915</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -932,13 +932,13 @@
         <v>-12.22423203642506</v>
       </c>
       <c r="E24">
-        <v>-26.42347130097784</v>
+        <v>-23.02209371755056</v>
       </c>
       <c r="F24">
-        <v>0.4155915020355018</v>
+        <v>0.8538377703677366</v>
       </c>
       <c r="G24">
-        <v>-3.983679914439532</v>
+        <v>-2.825555078981831</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -955,13 +955,13 @@
         <v>-11.74595401615227</v>
       </c>
       <c r="E25">
-        <v>-27.25302886902095</v>
+        <v>-23.7299259042675</v>
       </c>
       <c r="F25">
-        <v>0.3196759369728271</v>
+        <v>0.9867613752624003</v>
       </c>
       <c r="G25">
-        <v>-4.180581231478764</v>
+        <v>-3.372718735167034</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -978,13 +978,13 @@
         <v>-11.26308088063584</v>
       </c>
       <c r="E26">
-        <v>-26.97045209094232</v>
+        <v>-23.82158221818274</v>
       </c>
       <c r="F26">
-        <v>0.4340004995965699</v>
+        <v>0.6492625587408459</v>
       </c>
       <c r="G26">
-        <v>-4.63974396613906</v>
+        <v>-3.017232355160094</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -1001,13 +1001,13 @@
         <v>-10.80286928479578</v>
       </c>
       <c r="E27">
-        <v>-26.67689376339509</v>
+        <v>-23.93615713905081</v>
       </c>
       <c r="F27">
-        <v>0.1226835092690606</v>
+        <v>1.043548318272313</v>
       </c>
       <c r="G27">
-        <v>-3.764386067372669</v>
+        <v>-3.68234743836399</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -1024,13 +1024,13 @@
         <v>-10.38659740952014</v>
       </c>
       <c r="E28">
-        <v>-27.24634031291162</v>
+        <v>-23.47858201141977</v>
       </c>
       <c r="F28">
-        <v>0.3076952017225277</v>
+        <v>0.7838015436692579</v>
       </c>
       <c r="G28">
-        <v>-4.828153733870061</v>
+        <v>-3.458206952627634</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -1047,13 +1047,13 @@
         <v>-10.02835066547762</v>
       </c>
       <c r="E29">
-        <v>-28.55748750624845</v>
+        <v>-23.2273920866883</v>
       </c>
       <c r="F29">
-        <v>0.1502209877267217</v>
+        <v>0.9430891009382421</v>
       </c>
       <c r="G29">
-        <v>-4.198709778851812</v>
+        <v>-2.872889259102331</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -1070,13 +1070,13 @@
         <v>-9.734576525531086</v>
       </c>
       <c r="E30">
-        <v>-28.1335589404944</v>
+        <v>-24.5953172871333</v>
       </c>
       <c r="F30">
-        <v>0.2890470645682282</v>
+        <v>0.2144465974214531</v>
       </c>
       <c r="G30">
-        <v>-3.748366337508136</v>
+        <v>-2.274395594330728</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -1093,13 +1093,13 @@
         <v>-9.503404999171238</v>
       </c>
       <c r="E31">
-        <v>-27.46574487858325</v>
+        <v>-23.99824251769597</v>
       </c>
       <c r="F31">
-        <v>0.1339040656799491</v>
+        <v>0.5237760368250859</v>
       </c>
       <c r="G31">
-        <v>-3.610657574711072</v>
+        <v>-2.90355153188706</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -1116,13 +1116,13 @@
         <v>-9.327407496641253</v>
       </c>
       <c r="E32">
-        <v>-28.05683753385645</v>
+        <v>-22.49254755251561</v>
       </c>
       <c r="F32">
-        <v>0.395088053401265</v>
+        <v>0.2616038166125357</v>
       </c>
       <c r="G32">
-        <v>-3.899128581366545</v>
+        <v>-3.094232333858002</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -1139,13 +1139,13 @@
         <v>-9.200347671559609</v>
       </c>
       <c r="E33">
-        <v>-27.49705927634629</v>
+        <v>-23.8993089460504</v>
       </c>
       <c r="F33">
-        <v>0.1724934358685044</v>
+        <v>0.5114540129500093</v>
       </c>
       <c r="G33">
-        <v>-3.705471598955798</v>
+        <v>-2.758102713619181</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -1162,13 +1162,13 @@
         <v>-9.112905544747527</v>
       </c>
       <c r="E34">
-        <v>-27.00957810636859</v>
+        <v>-23.56151195592224</v>
       </c>
       <c r="F34">
-        <v>-0.2208516023491912</v>
+        <v>0.4569737376059346</v>
       </c>
       <c r="G34">
-        <v>-3.421509555324813</v>
+        <v>-2.523712778893242</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -1185,13 +1185,13 @@
         <v>-9.054319110079661</v>
       </c>
       <c r="E35">
-        <v>-26.89742139062062</v>
+        <v>-22.34231542731115</v>
       </c>
       <c r="F35">
-        <v>-0.0980779686665789</v>
+        <v>0.5911421353501337</v>
       </c>
       <c r="G35">
-        <v>-3.480179043371777</v>
+        <v>-1.952627120641266</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -1208,13 +1208,13 @@
         <v>-9.012448038082242</v>
       </c>
       <c r="E36">
-        <v>-26.9037838966014</v>
+        <v>-23.56419734100878</v>
       </c>
       <c r="F36">
-        <v>-0.09526926622554704</v>
+        <v>0.5040953234139199</v>
       </c>
       <c r="G36">
-        <v>-2.625167757489746</v>
+        <v>-1.816262439333146</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -1231,13 +1231,13 @@
         <v>-8.972914257894807</v>
       </c>
       <c r="E37">
-        <v>-26.06025145777062</v>
+        <v>-22.45995612508241</v>
       </c>
       <c r="F37">
-        <v>0.2672837778782594</v>
+        <v>0.7090696289315013</v>
       </c>
       <c r="G37">
-        <v>-2.821238127598622</v>
+        <v>-1.527185602843986</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -1254,13 +1254,13 @@
         <v>-8.922690346639602</v>
       </c>
       <c r="E38">
-        <v>-25.74158274185085</v>
+        <v>-21.80634788613333</v>
       </c>
       <c r="F38">
-        <v>0.01850099932779197</v>
+        <v>0.5889059425975331</v>
       </c>
       <c r="G38">
-        <v>-2.72303741526722</v>
+        <v>-1.849079877263941</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -1277,13 +1277,13 @@
         <v>-8.85507268698823</v>
       </c>
       <c r="E39">
-        <v>-25.90768263997819</v>
+        <v>-21.03337360081606</v>
       </c>
       <c r="F39">
-        <v>0.3155986860935283</v>
+        <v>0.6492625587408459</v>
       </c>
       <c r="G39">
-        <v>-2.355791977504789</v>
+        <v>-0.8041094883385304</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -1300,13 +1300,13 @@
         <v>-8.768277034766497</v>
       </c>
       <c r="E40">
-        <v>-25.09624802491378</v>
+        <v>-20.88469474219622</v>
       </c>
       <c r="F40">
-        <v>0.03874076092710811</v>
+        <v>0.5890453087180919</v>
       </c>
       <c r="G40">
-        <v>-2.351994781771245</v>
+        <v>-1.471412842143884</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -1323,13 +1323,13 @@
         <v>-8.664505924024009</v>
       </c>
       <c r="E41">
-        <v>-25.97299229211681</v>
+        <v>-21.1013550526192</v>
       </c>
       <c r="F41">
-        <v>0.08036451164964539</v>
+        <v>0.6872319080635068</v>
       </c>
       <c r="G41">
-        <v>-2.355427817495469</v>
+        <v>-1.65580691813575</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -1346,13 +1346,13 @@
         <v>-8.548587468198956</v>
       </c>
       <c r="E42">
-        <v>-25.40658434865943</v>
+        <v>-21.73735205615246</v>
       </c>
       <c r="F42">
-        <v>0.1449527899990124</v>
+        <v>0.8265220107382371</v>
       </c>
       <c r="G42">
-        <v>-2.824307003313526</v>
+        <v>-1.276040997143795</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -1369,13 +1369,13 @@
         <v>-8.423838962342865</v>
       </c>
       <c r="E43">
-        <v>-24.35182123974086</v>
+        <v>-20.5119107618848</v>
       </c>
       <c r="F43">
-        <v>0.1607732202412947</v>
+        <v>0.9738161631095983</v>
       </c>
       <c r="G43">
-        <v>-2.463229111890757</v>
+        <v>-1.783653565771325</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -1392,13 +1392,13 @@
         <v>-8.292110483595874</v>
       </c>
       <c r="E44">
-        <v>-24.35452021024944</v>
+        <v>-19.94076150614138</v>
       </c>
       <c r="F44">
-        <v>0.302168068077644</v>
+        <v>0.7054033497372589</v>
       </c>
       <c r="G44">
-        <v>-2.873336182750132</v>
+        <v>-1.624462672969931</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -1415,13 +1415,13 @@
         <v>-8.156957574827537</v>
       </c>
       <c r="E45">
-        <v>-24.6489842325982</v>
+        <v>-20.0221834687993</v>
       </c>
       <c r="F45">
-        <v>0.3613622440790243</v>
+        <v>0.7231408559901807</v>
       </c>
       <c r="G45">
-        <v>-2.864142797787576</v>
+        <v>-1.730770911327007</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -1438,13 +1438,13 @@
         <v>-8.026034982482891</v>
       </c>
       <c r="E46">
-        <v>-24.75563432395285</v>
+        <v>-19.47537476084711</v>
       </c>
       <c r="F46">
-        <v>0.3808061934558321</v>
+        <v>0.9830206618901324</v>
       </c>
       <c r="G46">
-        <v>-3.290458299607224</v>
+        <v>-2.281999917434435</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -1461,13 +1461,13 @@
         <v>-7.908527331063985</v>
       </c>
       <c r="E47">
-        <v>-23.84042972700267</v>
+        <v>-19.29059490743813</v>
       </c>
       <c r="F47">
-        <v>0.2393986759721592</v>
+        <v>1.105298595621212</v>
       </c>
       <c r="G47">
-        <v>-3.171517019472288</v>
+        <v>-1.872902562964537</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -1484,13 +1484,13 @@
         <v>-7.810555572096185</v>
       </c>
       <c r="E48">
-        <v>-22.34798960524276</v>
+        <v>-18.9864127798689</v>
       </c>
       <c r="F48">
-        <v>0.402888596887762</v>
+        <v>0.9007471395830531</v>
       </c>
       <c r="G48">
-        <v>-4.226309797012717</v>
+        <v>-2.473511666335733</v>
       </c>
     </row>
     <row r="49" spans="1:7">
@@ -1507,13 +1507,13 @@
         <v>-7.73446255677367</v>
       </c>
       <c r="E49">
-        <v>-23.0687551137256</v>
+        <v>-19.35629853681542</v>
       </c>
       <c r="F49">
-        <v>0.2252300509996802</v>
+        <v>0.782007204867065</v>
       </c>
       <c r="G49">
-        <v>-3.302253773363647</v>
+        <v>-3.132886263574533</v>
       </c>
     </row>
     <row r="50" spans="1:7">
@@ -1530,13 +1530,13 @@
         <v>-7.680821228109612</v>
       </c>
       <c r="E50">
-        <v>-22.89709877799085</v>
+        <v>-19.14186623560421</v>
       </c>
       <c r="F50">
-        <v>0.53435915160501</v>
+        <v>0.9485465515228464</v>
       </c>
       <c r="G50">
-        <v>-3.783557436590588</v>
+        <v>-2.889385707524519</v>
       </c>
     </row>
     <row r="51" spans="1:7">
@@ -1553,13 +1553,13 @@
         <v>-7.651099852633985</v>
       </c>
       <c r="E51">
-        <v>-21.7632911552684</v>
+        <v>-18.68170082084078</v>
       </c>
       <c r="F51">
-        <v>0.6488064514371994</v>
+        <v>0.8597449934323257</v>
       </c>
       <c r="G51">
-        <v>-4.566716642088276</v>
+        <v>-2.767547700042722</v>
       </c>
     </row>
     <row r="52" spans="1:7">
@@ -1576,13 +1576,13 @@
         <v>-7.647968676744337</v>
       </c>
       <c r="E52">
-        <v>-21.24657415709718</v>
+        <v>-16.81235580742247</v>
       </c>
       <c r="F52">
-        <v>0.3101214391849809</v>
+        <v>1.110800389971449</v>
       </c>
       <c r="G52">
-        <v>-4.096202046773819</v>
+        <v>-3.349786586216502</v>
       </c>
     </row>
     <row r="53" spans="1:7">
@@ -1599,13 +1599,13 @@
         <v>-7.671562731357869</v>
       </c>
       <c r="E53">
-        <v>-22.00985297956402</v>
+        <v>-18.31810964276493</v>
       </c>
       <c r="F53">
-        <v>0.2540154897187076</v>
+        <v>1.071432628325455</v>
       </c>
       <c r="G53">
-        <v>-4.247619778649005</v>
+        <v>-3.068962939756745</v>
       </c>
     </row>
     <row r="54" spans="1:7">
@@ -1622,13 +1622,13 @@
         <v>-7.721055998849431</v>
       </c>
       <c r="E54">
-        <v>-20.56761552065315</v>
+        <v>-16.56900467119828</v>
       </c>
       <c r="F54">
-        <v>0.6825979845549309</v>
+        <v>1.108632296573212</v>
       </c>
       <c r="G54">
-        <v>-4.73999390615927</v>
+        <v>-2.978148054523458</v>
       </c>
     </row>
     <row r="55" spans="1:7">
@@ -1645,13 +1645,13 @@
         <v>-7.795800744483788</v>
       </c>
       <c r="E55">
-        <v>-21.20720360407449</v>
+        <v>-16.28951631239288</v>
       </c>
       <c r="F55">
-        <v>0.4291923684372958</v>
+        <v>0.8529303068781898</v>
       </c>
       <c r="G55">
-        <v>-4.676457916169577</v>
+        <v>-3.696241797992311</v>
       </c>
     </row>
     <row r="56" spans="1:7">
@@ -1668,13 +1668,13 @@
         <v>-7.893429310671662</v>
       </c>
       <c r="E56">
-        <v>-20.80682763163433</v>
+        <v>-17.26906599651805</v>
       </c>
       <c r="F56">
-        <v>0.1294047571741856</v>
+        <v>0.7587378138515132</v>
       </c>
       <c r="G56">
-        <v>-4.905501319849593</v>
+        <v>-3.749213837166189</v>
       </c>
     </row>
     <row r="57" spans="1:7">
@@ -1691,13 +1691,13 @@
         <v>-8.011432245535262</v>
       </c>
       <c r="E57">
-        <v>-20.50841930842489</v>
+        <v>-16.0245643551521</v>
       </c>
       <c r="F57">
-        <v>0.1239599762369048</v>
+        <v>0.5580585187766036</v>
       </c>
       <c r="G57">
-        <v>-5.006684833711878</v>
+        <v>-3.966431972179929</v>
       </c>
     </row>
     <row r="58" spans="1:7">
@@ -1714,13 +1714,13 @@
         <v>-8.146539056893099</v>
       </c>
       <c r="E58">
-        <v>-20.71207836997185</v>
+        <v>-15.16884126429268</v>
       </c>
       <c r="F58">
-        <v>0.2867950347564733</v>
+        <v>0.8114467141291689</v>
       </c>
       <c r="G58">
-        <v>-5.059120564508395</v>
+        <v>-4.371934074194177</v>
       </c>
     </row>
     <row r="59" spans="1:7">
@@ -1737,13 +1737,13 @@
         <v>-8.294811374219327</v>
       </c>
       <c r="E59">
-        <v>-19.77040484244683</v>
+        <v>-14.40106566713621</v>
       </c>
       <c r="F59">
-        <v>0.3166708549982808</v>
+        <v>0.4384317087479696</v>
       </c>
       <c r="G59">
-        <v>-4.485009067633524</v>
+        <v>-3.921193367385788</v>
       </c>
     </row>
     <row r="60" spans="1:7">
@@ -1760,13 +1760,13 @@
         <v>-8.453143284364195</v>
       </c>
       <c r="E60">
-        <v>-20.30876794637472</v>
+        <v>-15.40898171244543</v>
       </c>
       <c r="F60">
-        <v>0.09444524094381751</v>
+        <v>0.5002738410399645</v>
       </c>
       <c r="G60">
-        <v>-5.220652013006053</v>
+        <v>-4.942797925895023</v>
       </c>
     </row>
     <row r="61" spans="1:7">
@@ -1783,13 +1783,13 @@
         <v>-8.620160391500754</v>
       </c>
       <c r="E61">
-        <v>-20.16320920634617</v>
+        <v>-15.15348520893267</v>
       </c>
       <c r="F61">
-        <v>0.113938285204004</v>
+        <v>0.4355897484827134</v>
       </c>
       <c r="G61">
-        <v>-5.888346011185042</v>
+        <v>-4.060236280035178</v>
       </c>
     </row>
     <row r="62" spans="1:7">
@@ -1806,13 +1806,13 @@
         <v>-8.795755105494358</v>
       </c>
       <c r="E62">
-        <v>-20.29324433747642</v>
+        <v>-15.64171357712163</v>
       </c>
       <c r="F62">
-        <v>0.290869910076899</v>
+        <v>0.8776123635703136</v>
       </c>
       <c r="G62">
-        <v>-5.868827034685498</v>
+        <v>-4.17583059862991</v>
       </c>
     </row>
     <row r="63" spans="1:7">
@@ -1829,13 +1829,13 @@
         <v>-8.982923378924676</v>
       </c>
       <c r="E63">
-        <v>-18.98413948591705</v>
+        <v>-14.91073183127749</v>
       </c>
       <c r="F63">
-        <v>-0.1702807050573787</v>
+        <v>0.1049412518983925</v>
       </c>
       <c r="G63">
-        <v>-5.977005731272263</v>
+        <v>-5.260613608210596</v>
       </c>
     </row>
     <row r="64" spans="1:7">
@@ -1852,13 +1852,13 @@
         <v>-9.186276919371256</v>
       </c>
       <c r="E64">
-        <v>-18.89273676654623</v>
+        <v>-13.9769242631038</v>
       </c>
       <c r="F64">
-        <v>-0.1735328451547337</v>
+        <v>0.7187207327801892</v>
       </c>
       <c r="G64">
-        <v>-7.058825802595301</v>
+        <v>-5.145198059074985</v>
       </c>
     </row>
     <row r="65" spans="1:7">
@@ -1875,13 +1875,13 @@
         <v>-9.409169239773876</v>
       </c>
       <c r="E65">
-        <v>-18.86076574005208</v>
+        <v>-14.03698088539352</v>
       </c>
       <c r="F65">
-        <v>0.1799566499950128</v>
+        <v>0.39070039616254</v>
       </c>
       <c r="G65">
-        <v>-6.453899747840895</v>
+        <v>-6.286313311551909</v>
       </c>
     </row>
     <row r="66" spans="1:7">
@@ -1898,13 +1898,13 @@
         <v>-9.651413439708938</v>
       </c>
       <c r="E66">
-        <v>-19.84996560228759</v>
+        <v>-14.21322003682404</v>
       </c>
       <c r="F66">
-        <v>0.07815445004464965</v>
+        <v>0.3904707588048013</v>
       </c>
       <c r="G66">
-        <v>-6.811561156267136</v>
+        <v>-4.926874201851128</v>
       </c>
     </row>
     <row r="67" spans="1:7">
@@ -1921,13 +1921,13 @@
         <v>-9.909907281106811</v>
       </c>
       <c r="E67">
-        <v>-18.52099433525657</v>
+        <v>-14.49342842299666</v>
       </c>
       <c r="F67">
-        <v>-0.1833090617707414</v>
+        <v>0.2364133903215559</v>
       </c>
       <c r="G67">
-        <v>-6.67432249093665</v>
+        <v>-5.730558789692298</v>
       </c>
     </row>
     <row r="68" spans="1:7">
@@ -1944,13 +1944,13 @@
         <v>-10.17897945016449</v>
       </c>
       <c r="E68">
-        <v>-18.32411892777311</v>
+        <v>-13.80553057886149</v>
       </c>
       <c r="F68">
-        <v>-0.121699734248316</v>
+        <v>0.1723556534538611</v>
       </c>
       <c r="G68">
-        <v>-7.006416556163099</v>
+        <v>-4.837757626479487</v>
       </c>
     </row>
     <row r="69" spans="1:7">
@@ -1967,13 +1967,13 @@
         <v>-10.45071964456706</v>
       </c>
       <c r="E69">
-        <v>-18.37363779104698</v>
+        <v>-14.17480046334296</v>
       </c>
       <c r="F69">
-        <v>-0.2409021110916123</v>
+        <v>0.4621477048316753</v>
       </c>
       <c r="G69">
-        <v>-7.297582346887539</v>
+        <v>-6.585781950488841</v>
       </c>
     </row>
     <row r="70" spans="1:7">
@@ -1990,13 +1990,13 @@
         <v>-10.71737737432664</v>
       </c>
       <c r="E70">
-        <v>-18.5453892247359</v>
+        <v>-12.99761005962703</v>
       </c>
       <c r="F70">
-        <v>-0.3570859444600811</v>
+        <v>0.1309021511172336</v>
       </c>
       <c r="G70">
-        <v>-7.494516769382164</v>
+        <v>-6.304567659655451</v>
       </c>
     </row>
     <row r="71" spans="1:7">
@@ -2013,13 +2013,13 @@
         <v>-10.97142585355867</v>
       </c>
       <c r="E71">
-        <v>-18.04979755781046</v>
+        <v>-14.16335248105157</v>
       </c>
       <c r="F71">
-        <v>-0.1151384406406504</v>
+        <v>0.5251506935596874</v>
       </c>
       <c r="G71">
-        <v>-7.487236879741308</v>
+        <v>-6.267996063083122</v>
       </c>
     </row>
     <row r="72" spans="1:7">
@@ -2036,13 +2036,13 @@
         <v>-11.20469594477334</v>
       </c>
       <c r="E72">
-        <v>-19.08075900734471</v>
+        <v>-14.1879873796533</v>
       </c>
       <c r="F72">
-        <v>-0.09885477641810196</v>
+        <v>0.2439375771258087</v>
       </c>
       <c r="G72">
-        <v>-8.064453668332014</v>
+        <v>-6.837366858745756</v>
       </c>
     </row>
     <row r="73" spans="1:7">
@@ -2059,13 +2059,13 @@
         <v>-11.4103624258382</v>
       </c>
       <c r="E73">
-        <v>-18.69855580109733</v>
+        <v>-13.56803023105521</v>
       </c>
       <c r="F73">
-        <v>-0.3227717883902546</v>
+        <v>0.5306865375871059</v>
       </c>
       <c r="G73">
-        <v>-7.947545063158191</v>
+        <v>-5.613454862331658</v>
       </c>
     </row>
     <row r="74" spans="1:7">
@@ -2082,13 +2082,13 @@
         <v>-11.58344694970611</v>
       </c>
       <c r="E74">
-        <v>-19.19997108559663</v>
+        <v>-13.89508115236317</v>
       </c>
       <c r="F74">
-        <v>-0.5741660979952815</v>
+        <v>0.1487829827555027</v>
       </c>
       <c r="G74">
-        <v>-7.941291442634507</v>
+        <v>-6.466774459443121</v>
       </c>
     </row>
     <row r="75" spans="1:7">
@@ -2105,13 +2105,13 @@
         <v>-11.7188579300922</v>
       </c>
       <c r="E75">
-        <v>-19.36614343930809</v>
+        <v>-16.22418401788422</v>
       </c>
       <c r="F75">
-        <v>-0.2445992725512057</v>
+        <v>-0.1271627278036244</v>
       </c>
       <c r="G75">
-        <v>-7.938027244732786</v>
+        <v>-6.209154426668116</v>
       </c>
     </row>
     <row r="76" spans="1:7">
@@ -2128,13 +2128,13 @@
         <v>-11.81442907732734</v>
       </c>
       <c r="E76">
-        <v>-19.29356558638716</v>
+        <v>-14.52839729928389</v>
       </c>
       <c r="F76">
-        <v>-0.3986431795341699</v>
+        <v>-0.02033780454244503</v>
       </c>
       <c r="G76">
-        <v>-8.19837516703215</v>
+        <v>-6.610985133679313</v>
       </c>
     </row>
     <row r="77" spans="1:7">
@@ -2151,13 +2151,13 @@
         <v>-11.8695801684083</v>
       </c>
       <c r="E77">
-        <v>-19.14883555710201</v>
+        <v>-15.37426643070263</v>
       </c>
       <c r="F77">
-        <v>-0.7152600417076974</v>
+        <v>0.4801528573843064</v>
       </c>
       <c r="G77">
-        <v>-7.886157617223486</v>
+        <v>-6.747435889171453</v>
       </c>
     </row>
     <row r="78" spans="1:7">
@@ -2174,13 +2174,13 @@
         <v>-11.88370080889619</v>
       </c>
       <c r="E78">
-        <v>-20.39278925311303</v>
+        <v>-15.40355207211023</v>
       </c>
       <c r="F78">
-        <v>-0.4376023450539803</v>
+        <v>-0.08307156326483242</v>
       </c>
       <c r="G78">
-        <v>-8.130386493292139</v>
+        <v>-7.238462624647235</v>
       </c>
     </row>
     <row r="79" spans="1:7">
@@ -2197,13 +2197,13 @@
         <v>-11.85646982956042</v>
       </c>
       <c r="E79">
-        <v>-20.84239879496458</v>
+        <v>-16.14029403689213</v>
       </c>
       <c r="F79">
-        <v>-0.4570067017829021</v>
+        <v>0.1446328814040936</v>
       </c>
       <c r="G79">
-        <v>-8.728760978424328</v>
+        <v>-6.394045084490872</v>
       </c>
     </row>
     <row r="80" spans="1:7">
@@ -2220,13 +2220,13 @@
         <v>-11.78822430348863</v>
       </c>
       <c r="E80">
-        <v>-21.63054799668156</v>
+        <v>-14.87721659514672</v>
       </c>
       <c r="F80">
-        <v>-0.5632456538553688</v>
+        <v>0.001622653533996062</v>
       </c>
       <c r="G80">
-        <v>-8.75895315374248</v>
+        <v>-6.680258299088563</v>
       </c>
     </row>
     <row r="81" spans="1:7">
@@ -2243,13 +2243,13 @@
         <v>-11.67981431799956</v>
       </c>
       <c r="E81">
-        <v>-20.98030441392017</v>
+        <v>-17.67146619683964</v>
       </c>
       <c r="F81">
-        <v>-0.7743465257068277</v>
+        <v>-0.1276726811083959</v>
       </c>
       <c r="G81">
-        <v>-9.071121045368058</v>
+        <v>-6.685416129038747</v>
       </c>
     </row>
     <row r="82" spans="1:7">
@@ -2266,13 +2266,13 @@
         <v>-11.53432421416339</v>
       </c>
       <c r="E82">
-        <v>-22.25764202031573</v>
+        <v>-17.44893245562871</v>
       </c>
       <c r="F82">
-        <v>-0.4736419487186781</v>
+        <v>-0.2383190867435306</v>
       </c>
       <c r="G82">
-        <v>-8.424290105177556</v>
+        <v>-7.008283703847249</v>
       </c>
     </row>
     <row r="83" spans="1:7">
@@ -2289,13 +2289,13 @@
         <v>-11.35777621997417</v>
       </c>
       <c r="E83">
-        <v>-22.46320304094591</v>
+        <v>-18.72350769287959</v>
       </c>
       <c r="F83">
-        <v>-0.6460568443207398</v>
+        <v>-0.167906729890135</v>
       </c>
       <c r="G83">
-        <v>-8.462536837792756</v>
+        <v>-6.829719498550039</v>
       </c>
     </row>
     <row r="84" spans="1:7">
@@ -2312,13 +2312,13 @@
         <v>-11.15838107637401</v>
       </c>
       <c r="E84">
-        <v>-23.08443721921416</v>
+        <v>-19.99504885254534</v>
       </c>
       <c r="F84">
-        <v>-0.5610799360160054</v>
+        <v>-0.1700574025233018</v>
       </c>
       <c r="G84">
-        <v>-8.728645109330452</v>
+        <v>-7.24952315729394</v>
       </c>
     </row>
     <row r="85" spans="1:7">
@@ -2335,13 +2335,13 @@
         <v>-10.94539573915146</v>
       </c>
       <c r="E85">
-        <v>-24.90240669501545</v>
+        <v>-20.11176121314502</v>
       </c>
       <c r="F85">
-        <v>-0.2761641151518293</v>
+        <v>-0.04187778869833696</v>
       </c>
       <c r="G85">
-        <v>-8.591432928364279</v>
+        <v>-6.809588071125731</v>
       </c>
     </row>
     <row r="86" spans="1:7">
@@ -2358,13 +2358,13 @@
         <v>-10.72886830144905</v>
       </c>
       <c r="E86">
-        <v>-25.28337815633274</v>
+        <v>-21.59767580385988</v>
       </c>
       <c r="F86">
-        <v>-0.2861858061847302</v>
+        <v>0.1477068545859616</v>
       </c>
       <c r="G86">
-        <v>-8.135974694162428</v>
+        <v>-6.556831229747915</v>
       </c>
     </row>
     <row r="87" spans="1:7">
@@ -2381,13 +2381,13 @@
         <v>-10.51765015649543</v>
       </c>
       <c r="E87">
-        <v>-26.88801575010669</v>
+        <v>-21.91752645149564</v>
       </c>
       <c r="F87">
-        <v>-0.377297991205877</v>
+        <v>-0.2782427291658436</v>
       </c>
       <c r="G87">
-        <v>-8.220588927600661</v>
+        <v>-6.795753301317117</v>
       </c>
     </row>
     <row r="88" spans="1:7">
@@ -2404,13 +2404,13 @@
         <v>-10.31881252796192</v>
       </c>
       <c r="E88">
-        <v>-28.9280434773481</v>
+        <v>-23.03365944016615</v>
       </c>
       <c r="F88">
-        <v>-0.06856323337349166</v>
+        <v>0.2598253148694972</v>
       </c>
       <c r="G88">
-        <v>-9.001943885779447</v>
+        <v>-5.939338344126435</v>
       </c>
     </row>
     <row r="89" spans="1:7">
@@ -2427,13 +2427,13 @@
         <v>-10.138615082715</v>
       </c>
       <c r="E89">
-        <v>-30.03579426063041</v>
+        <v>-27.28465573149052</v>
       </c>
       <c r="F89">
-        <v>-0.2361145681092389</v>
+        <v>-0.2029525580928946</v>
       </c>
       <c r="G89">
-        <v>-8.105802382117512</v>
+        <v>-6.583570506068608</v>
       </c>
     </row>
     <row r="90" spans="1:7">
@@ -2450,13 +2450,13 @@
         <v>-9.983746375673201</v>
       </c>
       <c r="E90">
-        <v>-30.69401248611931</v>
+        <v>-27.62021112698488</v>
       </c>
       <c r="F90">
-        <v>0.07390299151465245</v>
+        <v>-0.07163087173169785</v>
       </c>
       <c r="G90">
-        <v>-8.437131711324389</v>
+        <v>-6.586202389772329</v>
       </c>
     </row>
     <row r="91" spans="1:7">
@@ -2473,13 +2473,13 @@
         <v>-9.85892191410603</v>
       </c>
       <c r="E91">
-        <v>-33.94537304685748</v>
+        <v>-28.29996677485426</v>
       </c>
       <c r="F91">
-        <v>-0.0004036981848087109</v>
+        <v>0.1061472439529996</v>
       </c>
       <c r="G91">
-        <v>-8.635655195677865</v>
+        <v>-6.472322933766939</v>
       </c>
     </row>
     <row r="92" spans="1:7">
@@ -2496,13 +2496,13 @@
         <v>-9.769083303492318</v>
       </c>
       <c r="E92">
-        <v>-35.24291217580127</v>
+        <v>-30.28764081409299</v>
       </c>
       <c r="F92">
-        <v>0.2231799436921439</v>
+        <v>0.5624026241026541</v>
       </c>
       <c r="G92">
-        <v>-8.326178777575715</v>
+        <v>-7.118402380120026</v>
       </c>
     </row>
     <row r="93" spans="1:7">
@@ -2519,13 +2519,13 @@
         <v>-9.719715976905162</v>
       </c>
       <c r="E93">
-        <v>-37.83456917157603</v>
+        <v>-33.67951313057817</v>
       </c>
       <c r="F93">
-        <v>0.1747620945923714</v>
+        <v>0.2742528757591506</v>
       </c>
       <c r="G93">
-        <v>-8.547697311244969</v>
+        <v>-6.108450941909026</v>
       </c>
     </row>
     <row r="94" spans="1:7">
@@ -2542,13 +2542,13 @@
         <v>-9.714054539354347</v>
       </c>
       <c r="E94">
-        <v>-38.58583168826352</v>
+        <v>-34.93934592069708</v>
       </c>
       <c r="F94">
-        <v>0.5494867105092877</v>
+        <v>0.5885416902369821</v>
       </c>
       <c r="G94">
-        <v>-8.132876023537671</v>
+        <v>-6.666367250005781</v>
       </c>
     </row>
     <row r="95" spans="1:7">
@@ -2565,13 +2565,13 @@
         <v>-9.754840063871432</v>
       </c>
       <c r="E95">
-        <v>-42.30870601962835</v>
+        <v>-38.17722068584041</v>
       </c>
       <c r="F95">
-        <v>0.4549560962696647</v>
+        <v>0.6384379288088173</v>
       </c>
       <c r="G95">
-        <v>-8.563141006185669</v>
+        <v>-6.449877435010681</v>
       </c>
     </row>
     <row r="96" spans="1:7">
@@ -2588,13 +2588,13 @@
         <v>-9.843267301081651</v>
       </c>
       <c r="E96">
-        <v>-43.47563942971691</v>
+        <v>-39.91245494152156</v>
       </c>
       <c r="F96">
-        <v>0.7852078745221681</v>
+        <v>1.014170573540911</v>
       </c>
       <c r="G96">
-        <v>-8.101697305648814</v>
+        <v>-6.307527287367559</v>
       </c>
     </row>
     <row r="97" spans="1:7">
@@ -2611,13 +2611,13 @@
         <v>-9.971963476124735</v>
       </c>
       <c r="E97">
-        <v>-45.9381352898449</v>
+        <v>-42.95833599416169</v>
       </c>
       <c r="F97">
-        <v>0.9465067383037604</v>
+        <v>1.060878812104966</v>
       </c>
       <c r="G97">
-        <v>-8.727963136949363</v>
+        <v>-5.67962935711615</v>
       </c>
     </row>
     <row r="98" spans="1:7">
@@ -2634,13 +2634,13 @@
         <v>-10.13166607966294</v>
       </c>
       <c r="E98">
-        <v>-48.25882425065969</v>
+        <v>-43.70940605070386</v>
       </c>
       <c r="F98">
-        <v>1.072078780338954</v>
+        <v>1.263141813095315</v>
       </c>
       <c r="G98">
-        <v>-8.932177449084845</v>
+        <v>-7.125625990486715</v>
       </c>
     </row>
     <row r="99" spans="1:7">
@@ -2657,13 +2657,13 @@
         <v>-10.30259992489283</v>
       </c>
       <c r="E99">
-        <v>-50.50354353152181</v>
+        <v>-47.8848175823662</v>
       </c>
       <c r="F99">
-        <v>1.182513761234378</v>
+        <v>1.152599140197642</v>
       </c>
       <c r="G99">
-        <v>-8.467353681552396</v>
+        <v>-7.199341908009667</v>
       </c>
     </row>
     <row r="100" spans="1:7">
@@ -2680,13 +2680,13 @@
         <v>-10.47008601702019</v>
       </c>
       <c r="E100">
-        <v>-53.18457222607496</v>
+        <v>-49.78466186822617</v>
       </c>
       <c r="F100">
-        <v>1.246397290451374</v>
+        <v>1.660777110637937</v>
       </c>
       <c r="G100">
-        <v>-8.291815314878081</v>
+        <v>-7.502521668496122</v>
       </c>
     </row>
     <row r="101" spans="1:7">
@@ -2703,13 +2703,13 @@
         <v>-10.60577753278246</v>
       </c>
       <c r="E101">
-        <v>-54.83292204732644</v>
+        <v>-52.74714880777805</v>
       </c>
       <c r="F101">
-        <v>1.326596158009228</v>
+        <v>1.580137972835591</v>
       </c>
       <c r="G101">
-        <v>-8.979998279399618</v>
+        <v>-7.15336174101473</v>
       </c>
     </row>
     <row r="102" spans="1:7">
@@ -2726,13 +2726,13 @@
         <v>-10.70972526633474</v>
       </c>
       <c r="E102">
-        <v>-58.19017984061549</v>
+        <v>-54.84434285877379</v>
       </c>
       <c r="F102">
-        <v>1.631003439427675</v>
+        <v>1.833426394715483</v>
       </c>
       <c r="G102">
-        <v>-8.816033579930593</v>
+        <v>-6.924566628250158</v>
       </c>
     </row>
   </sheetData>
